--- a/components/contract_submission_dates.xlsx
+++ b/components/contract_submission_dates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\components\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EAB32F-CA58-4F87-BECD-06AD6963210A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA7AE1B-45DC-4507-9E19-AEBBA7C4B671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E569A2E1-EAC3-4253-9F8F-490DCA030E3B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E569A2E1-EAC3-4253-9F8F-490DCA030E3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>Data date for Man &amp; Sub-contractor programme</t>
-  </si>
-  <si>
     <t>May</t>
   </si>
   <si>
@@ -62,19 +59,22 @@
     <t>December</t>
   </si>
   <si>
-    <t>Man Programme submission to client</t>
-  </si>
-  <si>
-    <t>Deadline for Man to accept / reject programme</t>
-  </si>
-  <si>
     <t>November</t>
   </si>
   <si>
-    <t>Sub contractor submits PFA to Man</t>
-  </si>
-  <si>
     <t>KEY</t>
+  </si>
+  <si>
+    <t>Data date for Murphy &amp; Sub-contractor programme</t>
+  </si>
+  <si>
+    <t>Sub contractor submits PFA to Murphy</t>
+  </si>
+  <si>
+    <t>Murphy Programme submission to client</t>
+  </si>
+  <si>
+    <t>Deadline for Murphy to accept / reject programme</t>
   </si>
 </sst>
 </file>
@@ -197,18 +197,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -217,9 +220,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,46 +564,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="16"/>
+      <c r="A1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="17"/>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
       <c r="F2" s="1">
         <v>1</v>
       </c>
@@ -630,13 +630,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
+      <c r="A3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="1">
         <v>15</v>
       </c>
@@ -663,14 +663,14 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="17">
+      <c r="A4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="2">
         <v>22</v>
       </c>
       <c r="G4" s="1">
@@ -696,13 +696,13 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
+      <c r="A5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
       <c r="F5" s="1">
         <v>29</v>
       </c>
